--- a/tests/fixtures/recomendaciones_4B.xlsx
+++ b/tests/fixtures/recomendaciones_4B.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recomendaciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="4° A" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,488 +413,640 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Colegio Manuel Bulnes Prieto</t>
+          <t>Indicadores que requieren refuerzo - 4° Básico</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colegio Manuel Bulnes Prieto</t>
+          <t>N° de pregunta</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OA evaluado</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>% de logro
+4° A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Unidad JUMP Math</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sugerencias metodológicas y/o didácticas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Análisis adicional</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Indicador</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>OA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Unidad JUMP</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Recomendación didáctica</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Análisis adicional</t>
+          <t>Tomo 4.1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tomo 4.2</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Resuelven problemas no rutinarios en contextos cotidianos que incluyen dinero.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Tomo 4.1 U2 · Tomo 4.2 U3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Abordar estrategias de RP como el ensayo y error, transferir desde problemas similares ya resueltos, como también resolver problemas en contexto de dinero y representarlos usando monedas y/o billetes (jugar al supermercado).  Reforzar composición y descomposición de un número de tres cifras a partir de diversas combinaciones, por ejemplo: 850 = 300 + 300 + 250.  Uso de “Fichas de Monitoreo Diario” U2 (4.1).   Ejemplos de actividades para realizar en el inicio de al menos dos clases:   Materiales: imágenes de productos con precios y pizarras.  Clase 1 - ¿Alcanza o no alcanza?: Con un presupuesto de $1 000 y precios de $320, $450, $580 y $670, cada pareja elige dos productos, calcula el total y escribe total ≤ $1 000. Analizar también una elección que no alcance.  Clase 2 - Compra y vuelto: Usar nuevos precios ($250, $360, $540 y $690). Elegir dos productos, calcular el total y luego el vuelto mediante $1 000 - total. Registrar las dos operaciones y una respuesta escrita.  Comprobación: dos productos elegidos, total correcto, respeto del presupuesto y vuelto correcto.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>El DIA muestra 38% correcto pero 23% &lt;b&gt;parcialmente&lt;/b&gt; correcto: cerca de 6 de cada 10 estudiantes eligieron una estrategia y productos válidos, pero fallaron en la operatoria (cálculo del vuelto con canje). El cuello de botella no es comprender el problema, sino la fluidez de la adición/sustracción con canje. La caída de 32 pts frente al control JUMP de U2 (70%) se explica porque el ítem DIA es no rutinario y de varios pasos. Añadir: (1) priorizar precisión del cálculo con canje antes que la estrategia; (2) instalar la estimación previa y la verificación del vuelto (“¿es razonable?”) como rutina metacognitiva; (3) usar problemas con datos que sobran, no solo cálculo directo.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Resuelven problemas que requieren calcular sustracciones de fracciones con igual denominador.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>U4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Concepto aún no trabajado o en desarrollo.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Prerrequisito ya logrado: “fracciones parte-todo” (P6, 85%). Apoyarse en él al introducir la sustracción de fracciones con igual denominador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Realizan conversiones entre unidades de longitud.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>U6</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Concepto aún no trabajado o en desarrollo.    Uso de "Fichas de Monitoreo Diario" U6 (4.1).</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Distractor A muy fuerte (38%): apunta a una dirección o factor de conversión incorrectos (m↔cm). Al abordar U6, poner el énfasis en el factor correcto usando material graduado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ordenan números decimales.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>U5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Concepto aún no trabajado.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Distractor B (31%) refleja el error “más dígitos, mayor valor” (p. ej. 0,45 &gt; 0,5). Al enseñar U5, contrastar con material de valor posicional decimal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Calculan el área de un cuadrado.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>U6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Concepto aún no trabajado.   Se recomienda articular (Ver Proyecto de Articulación Curricular - Medición)   Uso de "Fichas de Monitoreo Diario" U6 (4.2).</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Al abordar U6, distinguir explícitamente área (superficie / conteo de cuadrículas) de perímetro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>31</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Interpretan información presentada en un gráfico de barra simple con escala.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>U8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Concepto aún no trabajado, aunque corresponde a conocimientos abordados en 3° Básico (OA25).  Se recomienda articular.   Uso de "Fichas de Monitoreo Diario" U8 (4.2).</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Al abordar U8, trabajar la lectura de la escala del gráfico, no solo la altura de la barra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Identifican representaciones de números decimales.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>U5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Concepto aún no trabajado.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Distractor B (27%): confusión entre representación fraccionaria y decimal. Reforzar la equivalencia al introducir U5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Identifican un patrón de formación de secuencias numéricas presentadas en tablas.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Trabajar con el tablero del 100 a la vista, estrategias de CM para contar a saltos de manera ascendente y descendente, utilizando una regla que incluya el patrón multiplicativo y uno de sus términos.   Error frecuente: buscar la diferencia solo entre los dos primeros términos de la secuencia.   Uso de “Fichas de Monitoreo Diario” U1 (4.1).   Ejemplos de actividades para realizar en el inicio de al menos dos clases:  Materiales: pizarras.   Clase 1 - Una regla para todos los pasos: Mostrar 3, 6, 12, 24. Probar las reglas "sumar 3" y "multiplicar por 2" en cada transición; descartar la que no funciona siempre. Preguntar: ¿La regla sirve también de 6 a 12 y de 12 a 24?  Clase 2: Comparar 8, 16, 24, 32 con 5, 10, 20, 40. Identificar si la regla es sumar una cantidad fija o multiplicar por 2 y completar dos términos.  Comprobación: aceptar la regla solo si el estudiante la verifica en todas las transiciones, no únicamente entre los dos primeros términos.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>El patrón en el DIA se presenta en &lt;b&gt;tabla&lt;/b&gt;, no como secuencia lineal: exige leer la relación entre términos, no solo el “salto siguiente”. El distractor B (23%) corresponde a continuar sumando el último salto en vez de identificar la regla constante. La caída del control U1 (81%) al DIA (58%) —23 pts— es coherente con el cambio de formato. Añadir: (1) pedir enunciar la regla en palabras (“cada término aumenta en ___”) antes de completar; (2) alternar tablas crecientes y decrecientes; (3) usar tablas donde el primer salto no sea evidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tomo 4.2 U4</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Calculan adiciones de fracciones con igual denominador.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>U4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Concepto aún no trabajado o en desarrollo.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Prerrequisito ya logrado: “fracciones parte-todo” (P6, 85%). Apoyarse en él al introducir la sustracción de fracciones con igual denominador.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Realizan conversiones entre unidades de longitud.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Tomo 4.1 U6</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Prerrequisito: fracciones parte-todo (logrado). Introducir la adición con igual denominador apoyándose en él.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Identifican figuras simétricas.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Se recomienda articular (Ver Proyecto de Articulación Curricular - Geometría).   Ejemplos de actividades para realizar en el inicio de al menos dos clases:  Materiales: cuadrícula, recortes o espejo.    Clase 1: Mostrar un cuadrado, un paralelogramo, un triángulo escaleno y un trapecio isósceles. Antes de verificar, cada estudiante predice cuáles son simétricos y dibuja un posible eje. Comprobar mediante plegado, recorte o espejo. Preguntar: ¿Los puntos correspondientes quedan a igual distancia del eje?  Clase 2: Completar en cuadrícula la mitad faltante de dos figuras y luego identificar la figura simétrica entre tres opciones.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Enseñado en U1 (4.2): control 78% → DIA 62% (−16 pts). Los distractores repartidos (B 15%, C 12%) sugieren confusión entre &lt;b&gt;eje de simetría&lt;/b&gt; y otras transformaciones (rotación/traslación). Añadir: (1) verificación concreta con doblado de papel y espejo (mira); (2) contrastar figuras simétricas con figuras “casi simétricas” (contraejemplos) para afinar el criterio; (3) marcar explícitamente el eje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Identifican figuras 2D relacionadas por una rotación.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>U7</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Concepto aún no trabajado, aunque corresponde a conocimientos abordados en 3° Básico (OA17).  Se recomienda articular (Ver Proyecto de Articulación Curricular - Geometría).   Ejemplos de actividades para realizar en el inicio de al menos dos clases:  Materiales: recorte de una figura con un punto marcado.   Clase 1 - Girar, no voltear: Trazar una figura marcada, rotarla 90° y 180° alrededor de un punto fijo sin darla vuelta y volver a trazarla. Comparar con una traslación y una reflexión. Preguntar: ¿Qué cambió y qué se mantuvo?  Clase 2: Mostrar tres pares de figuras: uno por rotación, uno por reflexión y uno por traslación. Identificar la transformación y justificar usando la posición del punto marcado y la orientación de los lados; verificar con el recorte.  Comprobación: reconoce la rotación y explica que la figura conserva forma y tamaño, pero cambia de orientación.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>24</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Resuelven inecuaciones aditivas de un paso que involucren adiciones y sustracciones.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Concepto aún no trabajado.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Consolidar primero las ecuaciones de un paso (P10, 85% logrado) antes de introducir inecuaciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>22</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Resuelven problemas que requieren calcular adiciones de números decimales.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>U5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Concepto aún no trabajado.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Amarillo alto (73%). Reforzar alineación por valor posicional al sumar decimales en U5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>28</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Resuelven problemas que requieren realizar conversiones de unidades de tiempo.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>U6</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Concepto aún no trabajado o en desarrollo.    Uso de "Fichas de Monitoreo Diario" U6 (4.1).</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Distractor A muy fuerte (38%): apunta a una dirección o factor de conversión incorrectos (m↔cm). Al abordar U6, poner el énfasis en el factor correcto usando material graduado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Ordenan números decimales.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Tomo 4.2 U5</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Concepto aún no trabajado.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Distractor B (31%) refleja el error “más dígitos, mayor valor” (p. ej. 0,45 &gt; 0,5). Al enseñar U5, contrastar con material de valor posicional decimal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Calculan el área de un cuadrado.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Tomo 4.2 U6</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Concepto aún no trabajado.   Se recomienda articular (Ver Proyecto de Articulación Curricular - Medición)   Uso de "Fichas de Monitoreo Diario" U6 (4.2).</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Al abordar U6, distinguir explícitamente área (superficie / conteo de cuadrículas) de perímetro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Interpretan información presentada en un gráfico de barra simple con escala.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Tomo 4.2 U8</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Concepto aún no trabajado, aunque corresponde a conocimientos abordados en 3° Básico (OA25).  Se recomienda articular.   Uso de "Fichas de Monitoreo Diario" U8 (4.2).</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Al abordar U8, trabajar la lectura de la escala del gráfico, no solo la altura de la barra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Identifican representaciones de números decimales.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Tomo 4.2 U5</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Concepto aún no trabajado.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Distractor B (27%): confusión entre representación fraccionaria y decimal. Reforzar la equivalencia al introducir U5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Identifican un patrón de formación de secuencias numéricas presentadas en tablas.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Tomo 4.1 U1 · Tomo 4.2 U3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Trabajar con el tablero del 100 a la vista, estrategias de CM para contar a saltos de manera ascendente y descendente, utilizando una regla que incluya el patrón multiplicativo y uno de sus términos.   Error frecuente: buscar la diferencia solo entre los dos primeros términos de la secuencia.   Uso de “Fichas de Monitoreo Diario” U1 (4.1).   Ejemplos de actividades para realizar en el inicio de al menos dos clases:  Materiales: pizarras.   Clase 1 - Una regla para todos los pasos: Mostrar 3, 6, 12, 24. Probar las reglas "sumar 3" y "multiplicar por 2" en cada transición; descartar la que no funciona siempre. Preguntar: ¿La regla sirve también de 6 a 12 y de 12 a 24?  Clase 2: Comparar 8, 16, 24, 32 con 5, 10, 20, 40. Identificar si la regla es sumar una cantidad fija o multiplicar por 2 y completar dos términos.  Comprobación: aceptar la regla solo si el estudiante la verifica en todas las transiciones, no únicamente entre los dos primeros términos.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>El patrón en el DIA se presenta en &lt;b&gt;tabla&lt;/b&gt;, no como secuencia lineal: exige leer la relación entre términos, no solo el “salto siguiente”. El distractor B (23%) corresponde a continuar sumando el último salto en vez de identificar la regla constante. La caída del control U1 (81%) al DIA (58%) —23 pts— es coherente con el cambio de formato. Añadir: (1) pedir enunciar la regla en palabras (“cada término aumenta en ___”) antes de completar; (2) alternar tablas crecientes y decrecientes; (3) usar tablas donde el primer salto no sea evidente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Calculan adiciones de fracciones con igual denominador.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Tomo 4.2 U4</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Concepto aún no trabajado o en desarrollo.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Prerrequisito: fracciones parte-todo (logrado). Introducir la adición con igual denominador apoyándose en él.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Identifican figuras simétricas.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Tomo 4.2 U1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Se recomienda articular (Ver Proyecto de Articulación Curricular - Geometría).   Ejemplos de actividades para realizar en el inicio de al menos dos clases:  Materiales: cuadrícula, recortes o espejo.    Clase 1: Mostrar un cuadrado, un paralelogramo, un triángulo escaleno y un trapecio isósceles. Antes de verificar, cada estudiante predice cuáles son simétricos y dibuja un posible eje. Comprobar mediante plegado, recorte o espejo. Preguntar: ¿Los puntos correspondientes quedan a igual distancia del eje?  Clase 2: Completar en cuadrícula la mitad faltante de dos figuras y luego identificar la figura simétrica entre tres opciones.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Enseñado en U1 (4.2): control 78% → DIA 62% (−16 pts). Los distractores repartidos (B 15%, C 12%) sugieren confusión entre &lt;b&gt;eje de simetría&lt;/b&gt; y otras transformaciones (rotación/traslación). Añadir: (1) verificación concreta con doblado de papel y espejo (mira); (2) contrastar figuras simétricas con figuras “casi simétricas” (contraejemplos) para afinar el criterio; (3) marcar explícitamente el eje.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Identifican figuras 2D relacionadas por una rotación.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Tomo 4.2 U7</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Concepto aún no trabajado, aunque corresponde a conocimientos abordados en 3° Básico (OA17).  Se recomienda articular (Ver Proyecto de Articulación Curricular - Geometría).   Ejemplos de actividades para realizar en el inicio de al menos dos clases:  Materiales: recorte de una figura con un punto marcado.   Clase 1 - Girar, no voltear: Trazar una figura marcada, rotarla 90° y 180° alrededor de un punto fijo sin darla vuelta y volver a trazarla. Comparar con una traslación y una reflexión. Preguntar: ¿Qué cambió y qué se mantuvo?  Clase 2: Mostrar tres pares de figuras: uno por rotación, uno por reflexión y uno por traslación. Identificar la transformación y justificar usando la posición del punto marcado y la orientación de los lados; verificar con el recorte.  Comprobación: reconoce la rotación y explica que la figura conserva forma y tamaño, pero cambia de orientación.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Resuelven inecuaciones aditivas de un paso que involucren adiciones y sustracciones.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tomo 4.2 U3</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Concepto aún no trabajado.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Consolidar primero las ecuaciones de un paso (P10, 85% logrado) antes de introducir inecuaciones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Resuelven problemas que requieren calcular adiciones de números decimales.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Tomo 4.2 U5</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Concepto aún no trabajado.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Amarillo alto (73%). Reforzar alineación por valor posicional al sumar decimales en U5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Resuelven problemas que requieren realizar conversiones de unidades de tiempo.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Tomo 4.1 U6</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Concepto aún no trabajado o en desarrollo.    Uso de "Fichas de Monitoreo Diario" U6 (4.1).</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Identifican vistas de figuras 3D.</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Tomo 4.2 U7</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>U7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Concepto aún no trabajado.   Se recomienda articular (Ver Proyecto de Articulación Curricular - Geometría).</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Leen mediciones del tiempo en relojes análogos.</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>U6</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Concepto aún no trabajado o en desarrollo, aunque corresponde a conocimientos abordados en 3° Básico (OA20).  Se recomienda articular (Ver Proyecto de Articulación Curricular - Medición).  Ejemplos de actividades para realizar en el inicio de al menos dos clases:  Materiales: reloj análogo manipulable o dibujado.  Clase 1: Contar los minutos de 5 en 5 alrededor del reloj. Situar el minutero en el 8 (40 minutos) y luego observar que la manecilla horaria ya pasó el 10, pero aún no llega al 11: son las 10:40. Preguntar: ¿Qué hora ya pasó? Practicar también 3:20.  Clase 2: Representar y escribir en formato digital 6:35 y 11:50; luego leer un reloj mostrado por el docente.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Tomo 4.1 U6</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Concepto aún no trabajado o en desarrollo, aunque corresponde a conocimientos abordados en 3° Básico (OA20).  Se recomienda articular (Ver Proyecto de Articulación Curricular - Medición).  Ejemplos de actividades para realizar en el inicio de al menos dos clases:  Materiales: reloj análogo manipulable o dibujado.  Clase 1: Contar los minutos de 5 en 5 alrededor del reloj. Situar el minutero en el 8 (40 minutos) y luego observar que la manecilla horaria ya pasó el 10, pero aún no llega al 11: son las 10:40. Preguntar: ¿Qué hora ya pasó? Practicar también 3:20.  Clase 2: Representar y escribir en formato digital 6:35 y 11:50; luego leer un reloj mostrado por el docente.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Registran mediciones del tiempo en relojes digitales.</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Tomo 4.1 U6</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>U6</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>Concepto aún no trabajado o en desarrollo.    Se recomienda articular como actividad cotidiana.   Uso de "Fichas de Monitoreo Diario" U6 (4.1).</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
